--- a/02-Excel-Dashboards/Projeto_Estoque_Papelaria.xlsx
+++ b/02-Excel-Dashboards/Projeto_Estoque_Papelaria.xlsx
@@ -8,13 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jessi\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5C6CF677-EAED-457B-8AF6-FF709A61CC34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F7463C0-3DCE-4DB9-B15A-731058A944EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{7AA11E1B-855E-40EB-BD76-41A436060D0D}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
+    <sheet name="Planilha2" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$2:$G$12</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -99,7 +103,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="169" formatCode="&quot;R$&quot;\ #,##0.00"/>
+    <numFmt numFmtId="164" formatCode="&quot;R$&quot;\ #,##0.00"/>
   </numFmts>
   <fonts count="15" x14ac:knownFonts="1">
     <font>
@@ -234,7 +238,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -327,23 +331,31 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="169" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
@@ -355,17 +367,17 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="5" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="169" fontId="3" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="9" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -374,7 +386,7 @@
     </xf>
     <xf numFmtId="44" fontId="7" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="12" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -388,24 +400,35 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="169" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="44" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="8" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
@@ -422,6 +445,977 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="pt-BR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="pt-BR" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0"/>
+              <a:t>Faturamento por Produto</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="1.4960902898058182E-2"/>
+          <c:y val="4.9955807224143563E-2"/>
+          <c:w val="0.96479435822660342"/>
+          <c:h val="0.78303407279569504"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Planilha1!$D$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:numFmt formatCode="&quot;R$&quot;\ #,##0" sourceLinked="0"/>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="pt-BR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>(Planilha1!$A$3,Planilha1!$A$4,Planilha1!$A$5,Planilha1!$A$6,Planilha1!$A$7,Planilha1!$A$8,Planilha1!$A$9,Planilha1!$A$10,Planilha1!$A$11,Planilha1!$A$12)</c:f>
+              <c:strCache>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>Mochila Escolar</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Caderno Capa Dura</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Agenda 2026</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Cola Branca</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Tesoura sem Ponta</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Caneta Azul</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Lápis Preto</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Borracha Branca</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Marca-Texto Amarelo</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Régua 30cm</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>(Planilha1!$D$3,Planilha1!$D$4,Planilha1!$D$5,Planilha1!$D$6,Planilha1!$D$7,Planilha1!$D$8,Planilha1!$D$9,Planilha1!$D$10,Planilha1!$D$11,Planilha1!$D$12)</c:f>
+              <c:numCache>
+                <c:formatCode>_("R$"* #,##0.00_);_("R$"* \(#,##0.00\);_("R$"* "-"??_);_(@_)</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>750</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>518</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>360</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>222.5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>150</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>125</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>120</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>105</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>103.5</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>96</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-A758-4F8A-9242-6841CE1D2B49}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="287169455"/>
+        <c:axId val="287173295"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="287169455"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="287173295"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="287173295"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="_(&quot;R$&quot;* #,##0.00_);_(&quot;R$&quot;* \(#,##0.00\);_(&quot;R$&quot;* &quot;-&quot;??_);_(@_)" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="287169455"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="pt-BR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.78740157499999996" l="0.511811024" r="0.511811024" t="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>316230</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>329566</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>333375</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>11431</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Gráfico 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3ADC576D-3836-4163-A062-60D96AED6D19}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -721,7 +1715,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5332C5DD-5301-48F3-8F4E-592B76881485}">
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.44140625" customWidth="1"/>
@@ -733,341 +1727,314 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="27.6" x14ac:dyDescent="0.45">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="16"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="15"/>
     </row>
     <row r="2" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="C2" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="D2" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="E2" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="13" t="s">
+      <c r="F2" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="21">
+      <c r="G2" s="20">
         <v>0.1</v>
       </c>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
     </row>
-    <row r="3" spans="1:11" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B3" s="2">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="C3" s="3">
-        <v>25.9</v>
-      </c>
-      <c r="D3" s="8">
+        <v>150</v>
+      </c>
+      <c r="D3" s="7">
         <f>B3*C3</f>
-        <v>518</v>
+        <v>750</v>
       </c>
       <c r="E3" s="4">
         <f>D3*$G$2</f>
-        <v>51.800000000000004</v>
-      </c>
-      <c r="F3" s="9"/>
+        <v>75</v>
+      </c>
+      <c r="F3" s="8"/>
       <c r="G3" s="1"/>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
     </row>
-    <row r="4" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B4" s="2">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="C4" s="3">
-        <v>2.5</v>
-      </c>
-      <c r="D4" s="8">
-        <f t="shared" ref="D4:D12" si="0">B4*C4</f>
-        <v>125</v>
+        <v>25.9</v>
+      </c>
+      <c r="D4" s="7">
+        <f>B4*C4</f>
+        <v>518</v>
       </c>
       <c r="E4" s="4">
         <f>D4*$G$2</f>
-        <v>12.5</v>
-      </c>
-      <c r="F4" s="9"/>
+        <v>51.800000000000004</v>
+      </c>
+      <c r="F4" s="8"/>
       <c r="G4" s="1"/>
-      <c r="H4" s="6"/>
-      <c r="I4" s="6"/>
     </row>
     <row r="5" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" s="2">
-        <v>100</v>
+      <c r="A5" s="37" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="37">
+        <v>8</v>
       </c>
       <c r="C5" s="3">
-        <v>1.2</v>
-      </c>
-      <c r="D5" s="8">
-        <f t="shared" si="0"/>
-        <v>120</v>
+        <v>45</v>
+      </c>
+      <c r="D5" s="7">
+        <f>B5*C5</f>
+        <v>360</v>
       </c>
       <c r="E5" s="4">
         <f>D5*$G$2</f>
-        <v>12</v>
-      </c>
-      <c r="F5" s="9"/>
+        <v>36</v>
+      </c>
+      <c r="F5" s="8"/>
       <c r="G5" s="1"/>
-      <c r="H5" s="6"/>
-      <c r="I5" s="6"/>
     </row>
     <row r="6" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B6" s="2">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C6" s="3">
-        <v>3.5</v>
-      </c>
-      <c r="D6" s="8">
-        <f t="shared" si="0"/>
-        <v>105</v>
+        <v>8.9</v>
+      </c>
+      <c r="D6" s="7">
+        <f>B6*C6</f>
+        <v>222.5</v>
       </c>
       <c r="E6" s="4">
         <f>D6*$G$2</f>
-        <v>10.5</v>
-      </c>
-      <c r="F6" s="9"/>
+        <v>22.25</v>
+      </c>
+      <c r="F6" s="8"/>
       <c r="G6" s="1"/>
-      <c r="H6" s="6"/>
-      <c r="I6" s="6"/>
     </row>
-    <row r="7" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B7" s="2">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C7" s="3">
+        <v>12.5</v>
+      </c>
+      <c r="D7" s="7">
+        <f>B7*C7</f>
         <v>150</v>
-      </c>
-      <c r="D7" s="8">
-        <f t="shared" si="0"/>
-        <v>750</v>
       </c>
       <c r="E7" s="4">
         <f>D7*$G$2</f>
-        <v>75</v>
-      </c>
-      <c r="F7" s="9"/>
+        <v>15</v>
+      </c>
+      <c r="F7" s="8"/>
       <c r="G7" s="1"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="6"/>
     </row>
     <row r="8" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B8" s="2">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="C8" s="3">
-        <v>4.8</v>
-      </c>
-      <c r="D8" s="8">
-        <f t="shared" si="0"/>
-        <v>96</v>
+        <v>2.5</v>
+      </c>
+      <c r="D8" s="7">
+        <f>B8*C8</f>
+        <v>125</v>
       </c>
       <c r="E8" s="4">
         <f>D8*$G$2</f>
-        <v>9.6000000000000014</v>
-      </c>
-      <c r="F8" s="9"/>
+        <v>12.5</v>
+      </c>
+      <c r="F8" s="8"/>
       <c r="G8" s="1"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="6"/>
     </row>
-    <row r="9" spans="1:11" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B9" s="2">
-        <v>15</v>
+        <v>100</v>
       </c>
       <c r="C9" s="3">
-        <v>6.9</v>
-      </c>
-      <c r="D9" s="8">
-        <f t="shared" si="0"/>
-        <v>103.5</v>
+        <v>1.2</v>
+      </c>
+      <c r="D9" s="7">
+        <f>B9*C9</f>
+        <v>120</v>
       </c>
       <c r="E9" s="4">
         <f>D9*$G$2</f>
-        <v>10.350000000000001</v>
-      </c>
-      <c r="F9" s="9"/>
+        <v>12</v>
+      </c>
+      <c r="F9" s="8"/>
       <c r="G9" s="1"/>
-      <c r="H9" s="6"/>
-      <c r="I9" s="6"/>
     </row>
     <row r="10" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B10" s="2">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C10" s="3">
-        <v>8.9</v>
-      </c>
-      <c r="D10" s="8">
-        <f t="shared" si="0"/>
-        <v>222.5</v>
+        <v>3.5</v>
+      </c>
+      <c r="D10" s="7">
+        <f>B10*C10</f>
+        <v>105</v>
       </c>
       <c r="E10" s="4">
         <f>D10*$G$2</f>
-        <v>22.25</v>
-      </c>
-      <c r="F10" s="9"/>
+        <v>10.5</v>
+      </c>
+      <c r="F10" s="8"/>
       <c r="G10" s="1"/>
-      <c r="H10" s="6"/>
-      <c r="I10" s="6"/>
     </row>
     <row r="11" spans="1:11" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B11" s="2">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C11" s="3">
-        <v>12.5</v>
-      </c>
-      <c r="D11" s="8">
-        <f t="shared" si="0"/>
-        <v>150</v>
+        <v>6.9</v>
+      </c>
+      <c r="D11" s="7">
+        <f>B11*C11</f>
+        <v>103.5</v>
       </c>
       <c r="E11" s="4">
         <f>D11*$G$2</f>
-        <v>15</v>
-      </c>
-      <c r="F11" s="9"/>
+        <v>10.350000000000001</v>
+      </c>
+      <c r="F11" s="8"/>
       <c r="G11" s="1"/>
-      <c r="H11" s="6"/>
-      <c r="I11" s="6"/>
     </row>
     <row r="12" spans="1:11" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="B12" s="22">
+      <c r="A12" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="17">
-        <v>45</v>
-      </c>
-      <c r="D12" s="18">
-        <f t="shared" si="0"/>
-        <v>360</v>
-      </c>
-      <c r="E12" s="19">
+      <c r="B12" s="38">
+        <v>20</v>
+      </c>
+      <c r="C12" s="16">
+        <v>4.8</v>
+      </c>
+      <c r="D12" s="17">
+        <f>B12*C12</f>
+        <v>96</v>
+      </c>
+      <c r="E12" s="18">
         <f>D12*$G$2</f>
-        <v>36</v>
-      </c>
-      <c r="F12" s="12"/>
+        <v>9.6000000000000014</v>
+      </c>
+      <c r="F12" s="11"/>
       <c r="G12" s="5"/>
-      <c r="H12" s="10"/>
-      <c r="I12" s="6"/>
+      <c r="H12" s="9"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13" s="37" t="s">
+      <c r="A13" s="39"/>
+      <c r="B13" s="21"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="40"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="41"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="42"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A14" s="35" t="s">
         <v>14</v>
       </c>
-      <c r="B13" s="30"/>
-      <c r="C13" s="31">
+      <c r="B14" s="29"/>
+      <c r="C14" s="30">
         <f>AVERAGE(C3:C12)</f>
-        <v>26.120000000000005</v>
-      </c>
-      <c r="D13" s="23">
+        <v>26.119999999999997</v>
+      </c>
+      <c r="D14" s="22">
         <f>SUM(D3:D12)</f>
         <v>2550</v>
       </c>
-      <c r="E13" s="32">
-        <f>D13*$G$2</f>
+      <c r="E14" s="31">
+        <f>D14*$G$2</f>
         <v>255</v>
       </c>
-      <c r="F13" s="26"/>
-      <c r="G13" s="28"/>
-      <c r="H13" s="6"/>
-      <c r="I13" s="6"/>
-      <c r="K13" s="11"/>
+      <c r="F14" s="25"/>
+      <c r="G14" s="27"/>
+      <c r="K14" s="10"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A14" s="38" t="s">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A15" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="35"/>
-      <c r="C14" s="34">
+      <c r="B15" s="34"/>
+      <c r="C15" s="33">
         <f>MAX(C3:C12)</f>
         <v>150</v>
       </c>
-      <c r="D14" s="33"/>
-      <c r="E14" s="24"/>
-      <c r="F14" s="27"/>
-      <c r="G14" s="29"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="6"/>
-      <c r="K14" s="6"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A15" s="10"/>
-      <c r="B15" s="6"/>
-      <c r="C15" s="25"/>
-      <c r="D15" s="6"/>
-      <c r="E15" s="20"/>
-      <c r="F15" s="6"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
-      <c r="I15" s="6"/>
-      <c r="J15" s="6"/>
-      <c r="K15" s="6"/>
+      <c r="D15" s="32"/>
+      <c r="E15" s="23"/>
+      <c r="F15" s="26"/>
+      <c r="G15" s="28"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="H16" s="6"/>
-      <c r="I16" s="6"/>
-    </row>
-    <row r="18" spans="4:6" x14ac:dyDescent="0.3">
-      <c r="D18" s="6"/>
-    </row>
-    <row r="19" spans="4:6" x14ac:dyDescent="0.3">
-      <c r="D19" s="6"/>
-    </row>
-    <row r="20" spans="4:6" x14ac:dyDescent="0.3">
-      <c r="F20" s="36"/>
+      <c r="A16" s="9"/>
+      <c r="C16" s="24"/>
+      <c r="E16" s="19"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{903DA9DB-CF67-4C12-977C-810F2122136C}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>